--- a/data/weekly_mapping_recheck_targets.xlsx
+++ b/data/weekly_mapping_recheck_targets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AJ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,31 +610,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>청부입학</t>
+          <t>마귀공주</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851688&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852115&amp;tab=mon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>851688</t>
+          <t>852115</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:02</t>
+          <t>2026-06-29 13:06:04</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>강필</t>
+          <t>햄스터빵디</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -702,31 +702,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>유체를 이탈하였습니다</t>
+          <t>반도대탈출</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851839&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=851869&amp;tab=mon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>851839</t>
+          <t>851869</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:02</t>
+          <t>2026-06-29 13:06:04</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>이슬</t>
+          <t>카시모프</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -785,40 +785,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>대공가의 새아가는 조금 사나워요</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=851388&amp;tab=tue</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>851388</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:08</t>
+          <t>2026-06-29 13:06:06</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>심상</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -831,17 +831,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -855,36 +855,16 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -897,40 +877,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>듀오 레벨링</t>
+          <t>인그레이브</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851266&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=851854&amp;tab=tue</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>851266</t>
+          <t>851854</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:11</t>
+          <t>2026-06-29 13:06:07</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Karen Buchanan</t>
+          <t>도마</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -948,12 +928,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -967,36 +947,16 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1009,40 +969,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>재난은 늘 곁에 있다</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=827333&amp;tab=tue</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>827333</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:24</t>
+          <t>2026-06-29 13:06:08</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>이혜</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -1055,17 +1015,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1079,36 +1039,16 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1121,40 +1061,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>정권으로 세계최강</t>
+          <t>찬란한 유산 단편집</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851800&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>851800</t>
+          <t>849862</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:24</t>
+          <t>2026-06-29 13:06:10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>레블스튜디오</t>
+          <t>네이버웹툰</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1167,17 +1107,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>수, 토 연재</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1191,16 +1131,36 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI7" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1213,40 +1173,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>회귀자의 은퇴 라이프</t>
+          <t>호수의 백조</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=814509&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=851866&amp;tab=thu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>814509</t>
+          <t>851866</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:25</t>
+          <t>2026-06-29 13:06:12</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>서희</t>
+          <t>과일차</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1264,12 +1224,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1305,40 +1265,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>마법사가 죽음을 맞이하는 방법</t>
+          <t>숨이 차도 괜찮아</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=786269&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=850521&amp;tab=thu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>786269</t>
+          <t>850521</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:26</t>
+          <t>2026-06-29 13:06:14</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>박젶</t>
+          <t>황주영</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1356,12 +1316,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1397,63 +1357,55 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>중사의 드래곤</t>
+          <t>운명해주세요</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851032&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=835004&amp;tab=thu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>851032</t>
+          <t>835004</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:29</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>워티</t>
-        </is>
-      </c>
+          <t>2026-06-29 13:06:14</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1489,40 +1441,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>헤이트걸</t>
+          <t>연상녀클럽</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851934&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=851476&amp;tab=fri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>851934</t>
+          <t>851476</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:29</t>
+          <t>2026-06-29 13:06:16</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>나솔</t>
+          <t>한성만</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1540,12 +1492,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1581,40 +1533,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mickey x F1 정상을 향한 질주</t>
+          <t>지옥 최강 마금강</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=850745&amp;tab=fri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>849113</t>
+          <t>850745</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-22 11:41:29</t>
+          <t>2026-06-29 13:06:17</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Brandon Chen</t>
+          <t>최봉수</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1632,12 +1584,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1651,42 +1603,606 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr">
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>북설애담</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=827578&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>827578</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:18</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>휘요</t>
+        </is>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>78</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>찬란한 유산 단편집</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>849862</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:21</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>수, 토 연재</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>no_result</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
         <is>
           <t>needs_series_search</t>
         </is>
       </c>
-      <c r="AJ12" t="b">
+      <c r="AJ14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>80</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>데스루프</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>852086</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:21</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>97</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>결혼 청약 당첨</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=851265&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>851265</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:22</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>권계림</t>
+        </is>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>54</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>천도박멸</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852078&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>852078</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:24</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>와나나</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>107</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mickey x F1 정상을 향한 질주</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>849113</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:06:26</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Brandon Chen</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ18" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/weekly_mapping_recheck_targets.xlsx
+++ b/data/weekly_mapping_recheck_targets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ18"/>
+  <dimension ref="A1:AJ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,40 +601,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>마귀공주</t>
+          <t>레벨업! 여신님</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852115&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852169&amp;tab=tue</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>852115</t>
+          <t>852169</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:04</t>
+          <t>2026-07-06 12:42:05</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>햄스터빵디</t>
+          <t>도롱뇽</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -652,12 +652,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -693,40 +693,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>반도대탈출</t>
+          <t>찬란한 유산 단편집</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851869&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>851869</t>
+          <t>849862</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:04</t>
+          <t>2026-07-06 12:42:08</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>카시모프</t>
+          <t>네이버웹툰</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -739,17 +739,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>수, 토 연재</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -763,16 +763,36 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="Y3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -785,40 +805,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대공가의 새아가는 조금 사나워요</t>
+          <t>아이스크림 소년</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851388&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=834349&amp;tab=wed</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>851388</t>
+          <t>834349</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:06</t>
+          <t>2026-07-06 12:42:09</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>심상</t>
+          <t>은풀</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -836,12 +856,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -877,40 +897,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>인그레이브</t>
+          <t>반짝반짝 작은 눈</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851854&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=772729&amp;tab=wed</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>851854</t>
+          <t>772729</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:07</t>
+          <t>2026-07-06 12:42:09</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>도마</t>
+          <t>억수씨</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -928,12 +948,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -969,40 +989,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>재난은 늘 곁에 있다</t>
+          <t>대타용사</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=827333&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849541&amp;tab=thu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>827333</t>
+          <t>849541</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:08</t>
+          <t>2026-07-06 12:42:11</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>이혜</t>
+          <t>밭</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -1020,12 +1040,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1061,40 +1081,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>김오진과 이상한 동물들</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=838262&amp;tab=thu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>838262</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:10</t>
+          <t>2026-07-06 12:42:12</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>기선</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1107,17 +1127,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1131,36 +1151,16 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1173,40 +1173,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>호수의 백조</t>
+          <t>너를 울린 비밀</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851866&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=851715&amp;tab=fri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>851866</t>
+          <t>851715</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:12</t>
+          <t>2026-07-06 12:42:14</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>과일차</t>
+          <t>연수</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1265,40 +1265,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>숨이 차도 괜찮아</t>
+          <t>미운오리새끼</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=850521&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=839542&amp;tab=fri</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>850521</t>
+          <t>839542</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:14</t>
+          <t>2026-07-06 12:42:16</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>황주영</t>
+          <t>펀지르르</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1357,55 +1357,63 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>운명해주세요</t>
+          <t>찬란한 유산 단편집</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=835004&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>835004</t>
+          <t>849862</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:14</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>2026-07-06 12:42:18</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
       <c r="I10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>수, 토 연재</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1419,16 +1427,36 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
+      <c r="Y10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI10" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1441,40 +1469,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>연상녀클럽</t>
+          <t>쌍둥이에게 아내 자리를 빼앗겼다</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851476&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852058&amp;tab=sat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>851476</t>
+          <t>852058</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:16</t>
+          <t>2026-07-06 12:42:19</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>한성만</t>
+          <t>해민</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1492,12 +1520,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1533,40 +1561,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>지옥 최강 마금강</t>
+          <t>죽었는데 왜 집착하세요</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=850745&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=826529&amp;tab=sat</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>850745</t>
+          <t>826529</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:17</t>
+          <t>2026-07-06 12:42:19</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>최봉수</t>
+          <t>미카</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1584,12 +1612,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1625,40 +1653,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>북설애담</t>
+          <t>육각</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=827578&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=826660&amp;tab=sat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>827578</t>
+          <t>826660</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:18</t>
+          <t>2026-07-06 12:42:19</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>휘요</t>
+          <t>권라드</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1676,12 +1704,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1726,31 +1754,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>우리집에 온 여우들</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=837101&amp;tab=sat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>837101</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:21</t>
+          <t>2026-07-06 12:42:19</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>김현</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1763,17 +1791,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1787,36 +1815,16 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1829,55 +1837,63 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>데스루프</t>
+          <t>남들 로판 여주 할 때 나는 장롱 괴물 됨</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852086&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852333&amp;tab=sun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>852086</t>
+          <t>852333</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:21</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>2026-07-06 12:42:22</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>굿람</t>
+        </is>
+      </c>
       <c r="I15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1913,40 +1929,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>결혼 청약 당첨</t>
+          <t>Mickey x F1 정상을 향한 질주</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851265&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>851265</t>
+          <t>849113</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:22</t>
+          <t>2026-07-06 12:42:23</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>권계림</t>
+          <t>Brandon Chen</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1964,12 +1980,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1983,226 +1999,42 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
       <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI16" t="inlineStr">
         <is>
           <t>needs_series_search</t>
         </is>
       </c>
       <c r="AJ16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>54</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>천도박멸</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852078&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>852078</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-06-29 13:06:24</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>와나나</t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>107</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Mickey x F1 정상을 향한 질주</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>849113</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-06-29 13:06:26</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Brandon Chen</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ18" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/weekly_mapping_recheck_targets.xlsx
+++ b/data/weekly_mapping_recheck_targets.xlsx
@@ -601,40 +601,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>레벨업! 여신님</t>
+          <t>마귀공주</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852169&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852115&amp;tab=mon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>852169</t>
+          <t>852115</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:05</t>
+          <t>2026-07-13 11:55:47</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>도롱뇽</t>
+          <t>햄스터빵디</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -652,12 +652,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -693,40 +693,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>시냅틱 에러</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852168&amp;tab=tue</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>852168</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:08</t>
+          <t>2026-07-13 11:55:50</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>연제원</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -739,17 +739,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -763,36 +763,16 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -814,31 +794,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>아이스크림 소년</t>
+          <t>사라지게</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=834349&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852270&amp;tab=wed</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>834349</t>
+          <t>852270</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:09</t>
+          <t>2026-07-13 11:55:53</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>은풀</t>
+          <t>ㅎㅂㅆ</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -906,31 +886,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>반짝반짝 작은 눈</t>
+          <t>찬란한 유산 단편집</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=772729&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>772729</t>
+          <t>849862</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:09</t>
+          <t>2026-07-13 11:55:53</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>억수씨</t>
+          <t>네이버웹툰</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -943,17 +923,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>수, 토 연재</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -967,16 +947,36 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+      <c r="Y5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -989,40 +989,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대타용사</t>
+          <t>두 번 빼앗긴 남편</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849541&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=839880&amp;tab=wed</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>849541</t>
+          <t>839880</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:11</t>
+          <t>2026-07-13 11:55:54</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>밭</t>
+          <t>단주</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1090,31 +1090,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>김오진과 이상한 동물들</t>
+          <t>회귀한 천재 헌터의 슬기로운 청소생활</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=838262&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=796827&amp;tab=thu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>838262</t>
+          <t>796827</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:12</t>
+          <t>2026-07-13 11:55:57</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>기선</t>
+          <t>고일고일</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1182,31 +1182,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>너를 울린 비밀</t>
+          <t>홍색인간</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851715&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852170&amp;tab=fri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>851715</t>
+          <t>852170</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:14</t>
+          <t>2026-07-13 11:55:59</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>연수</t>
+          <t>퀴니니</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1265,40 +1265,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>미운오리새끼</t>
+          <t>블랙 옵스</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=839542&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852377&amp;tab=sat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>839542</t>
+          <t>852377</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:16</t>
+          <t>2026-07-13 11:56:04</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>펀지르르</t>
+          <t>신진우</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:18</t>
+          <t>2026-07-13 11:56:04</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1478,31 +1478,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>쌍둥이에게 아내 자리를 빼앗겼다</t>
+          <t>세레나</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852058&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=801475&amp;tab=sat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>852058</t>
+          <t>801475</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:19</t>
+          <t>2026-07-13 11:56:04</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>해민</t>
+          <t>정이나</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1570,31 +1570,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>죽었는데 왜 집착하세요</t>
+          <t>짜장 한 그릇에 제갈세가 데릴사위</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=826529&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=822114&amp;tab=sat</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>826529</t>
+          <t>822114</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:19</t>
+          <t>2026-07-13 11:56:06</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>미카</t>
+          <t>허일</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1653,40 +1653,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>육각</t>
+          <t>일타강사 백사부</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=826660&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=779632&amp;tab=sun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>826660</t>
+          <t>779632</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:19</t>
+          <t>2026-07-13 11:56:08</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>권라드</t>
+          <t>사내</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1745,40 +1745,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>우리집에 온 여우들</t>
+          <t>와인의 신</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=837101&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852403&amp;tab=sun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>837101</t>
+          <t>852403</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:19</t>
+          <t>2026-07-13 11:56:09</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>김현</t>
+          <t>성혜</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1846,31 +1846,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>남들 로판 여주 할 때 나는 장롱 괴물 됨</t>
+          <t>미래의 할 일</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852333&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852611&amp;tab=sun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>852333</t>
+          <t>852611</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:22</t>
+          <t>2026-07-13 11:56:10</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>굿람</t>
+          <t>복슬</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-06 12:42:23</t>
+          <t>2026-07-13 11:56:10</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">

--- a/data/weekly_mapping_recheck_targets.xlsx
+++ b/data/weekly_mapping_recheck_targets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ16"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,31 +610,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>마귀공주</t>
+          <t>환생천마</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852115&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=822657&amp;tab=mon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>852115</t>
+          <t>822657</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-13 11:55:47</t>
+          <t>2026-07-20 12:20:07</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>햄스터빵디</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -693,40 +693,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>시냅틱 에러</t>
+          <t>샤MONEY즘</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852168&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=840014&amp;tab=mon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>852168</t>
+          <t>840014</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-13 11:55:50</t>
+          <t>2026-07-20 12:20:07</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>연제원</t>
+          <t>나락</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -744,12 +744,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -785,40 +785,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>사라지게</t>
+          <t>시한부 천재가 살아남는 법</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852270&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=832703&amp;tab=mon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>852270</t>
+          <t>832703</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-13 11:55:53</t>
+          <t>2026-07-20 12:20:07</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ㅎㅂㅆ</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -836,12 +836,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -877,40 +877,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>절대검감</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=796075&amp;tab=mon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>796075</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-13 11:55:53</t>
+          <t>2026-07-20 12:20:07</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>김두루미</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -923,17 +923,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -947,36 +947,16 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -989,40 +969,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>두 번 빼앗긴 남편</t>
+          <t>백수세끼</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=839880&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=733074&amp;tab=mon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>839880</t>
+          <t>733074</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-13 11:55:54</t>
+          <t>2026-07-20 12:20:07</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>단주</t>
+          <t>치즈</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -1040,12 +1020,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1081,40 +1061,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>회귀한 천재 헌터의 슬기로운 청소생활</t>
+          <t>귀촌리</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=796827&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=822573&amp;tab=mon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>796827</t>
+          <t>822573</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-13 11:55:57</t>
+          <t>2026-07-20 12:20:07</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>고일고일</t>
+          <t>황양</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1132,12 +1112,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1173,40 +1153,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>홍색인간</t>
+          <t>소녀의 세계</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852170&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=654774&amp;tab=mon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>852170</t>
+          <t>654774</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-13 11:55:59</t>
+          <t>2026-07-20 12:20:07</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>퀴니니</t>
+          <t>모랑지</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1224,12 +1204,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1265,40 +1245,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>블랙 옵스</t>
+          <t>똑 닮은 딸</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852377&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=774866&amp;tab=mon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>852377</t>
+          <t>774866</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:04</t>
+          <t>2026-07-20 12:20:07</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>신진우</t>
+          <t>이담</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1316,12 +1296,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1357,40 +1337,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>파브르 in 사천당가</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=833702&amp;tab=mon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>833702</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:04</t>
+          <t>2026-07-20 12:20:07</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>지대공마법소년</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1403,17 +1383,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1427,36 +1407,16 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1469,40 +1429,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>세레나</t>
+          <t>회귀한 공작가의 막내도련님은 암살자</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=801475&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=821195&amp;tab=mon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>801475</t>
+          <t>821195</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:04</t>
+          <t>2026-07-20 12:20:07</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>정이나</t>
+          <t>스윙뱃</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1520,12 +1480,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1561,63 +1521,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>짜장 한 그릇에 제갈세가 데릴사위</t>
+          <t>그린스킨</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=822114&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=851187&amp;tab=mon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>822114</t>
+          <t>851187</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:06</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>허일</t>
-        </is>
-      </c>
+          <t>2026-07-20 12:20:08</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1653,40 +1605,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>일타강사 백사부</t>
+          <t>세림의 철칙</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=779632&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852516&amp;tab=mon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>779632</t>
+          <t>852516</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:08</t>
+          <t>2026-07-20 12:20:08</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>사내</t>
+          <t>세윤</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1704,12 +1656,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1745,40 +1697,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>와인의 신</t>
+          <t>시간을 돌아온 황후의 납치 결혼</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852403&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=834548&amp;tab=mon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>852403</t>
+          <t>834548</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:09</t>
+          <t>2026-07-20 12:20:09</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>성혜</t>
+          <t>그리온</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1796,12 +1748,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1837,40 +1789,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>미래의 할 일</t>
+          <t>공주는 헬스장에 간다</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852611&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852173&amp;tab=mon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>852611</t>
+          <t>852173</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:10</t>
+          <t>2026-07-20 12:20:09</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>복슬</t>
+          <t>콕</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1888,12 +1840,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1929,40 +1881,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mickey x F1 정상을 향한 질주</t>
+          <t>내가 죽인 드래곤과 결혼했다</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852628&amp;tab=tue</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>849113</t>
+          <t>852628</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-13 11:56:10</t>
+          <t>2026-07-20 12:20:12</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Brandon Chen</t>
+          <t>만둣불</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1980,12 +1932,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1999,42 +1951,1446 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr">
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>112</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>아폴론 저축은행</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=842845&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>842845</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:14</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>차무진</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>44</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>다 때려치고 콜라 팝니다</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852631&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>852631</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:15</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>윤재호</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>82</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>불로남친</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852783&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>852783</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:17</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>율로</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>85</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>찬란한 유산 단편집</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>849862</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:17</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>수, 토 연재</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr">
         <is>
           <t>no_result</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
         <is>
           <t>needs_series_search</t>
         </is>
       </c>
-      <c r="AJ16" t="b">
+      <c r="AJ20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>25</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>럭키비치</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>852498</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:19</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>thu,sun</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>thu,sun</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>85</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>좋은 하루 보내</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852274&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>852274</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:22</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>한구</t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>92</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>삼이는 재생한다</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=822874&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>822874</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:22</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>강은영</t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>104</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>일립예고 학생들</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=812962&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>812962</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:23</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>백본</t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>80</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>싸움 1티어 과외 쌤 구하기</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852547&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>852547</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:26</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>버퍼링</t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>68</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>황제의 검</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=813443&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>813443</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:30</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>레드훅</t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>83</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>찬란한 유산 단편집</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>849862</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:30</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>수, 토 연재</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>95</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>오싹한 연애</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852570&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>852570</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:31</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>꼉</t>
+        </is>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>20</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>럭키비치</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>852498</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:32</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>thu,sun</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>thu,sun</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>40</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>인간의 식탁</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852761&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>852761</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:33</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>김규삼</t>
+        </is>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>102</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Mickey x F1 정상을 향한 질주</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>849113</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:20:35</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Brandon Chen</t>
+        </is>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ31" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/weekly_mapping_recheck_targets.xlsx
+++ b/data/weekly_mapping_recheck_targets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ31"/>
+  <dimension ref="A1:AJ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,31 +610,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>환생천마</t>
+          <t>참교육</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=822657&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=758037&amp;tab=mon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>822657</t>
+          <t>758037</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:07</t>
+          <t>2026-07-27 12:19:44</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>채용택</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -702,46 +702,38 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>샤MONEY즘</t>
+          <t>신체</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=840014&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=844058&amp;tab=mon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>840014</t>
+          <t>844058</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:07</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>나락</t>
-        </is>
-      </c>
+          <t>2026-07-27 12:19:44</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>mon</t>
@@ -794,31 +786,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>시한부 천재가 살아남는 법</t>
+          <t>고블린 주식회사</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=832703&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852571&amp;tab=mon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>832703</t>
+          <t>852571</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:07</t>
+          <t>2026-07-27 12:19:46</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>살려주세요</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -886,31 +878,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>절대검감</t>
+          <t>수상한 다이어트 클럽</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=796075&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=821626&amp;tab=mon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>796075</t>
+          <t>821626</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:07</t>
+          <t>2026-07-27 12:19:46</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>김두루미</t>
+          <t>스프링</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -978,31 +970,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>백수세끼</t>
+          <t>다육이는 잘 자란다</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=733074&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=820800&amp;tab=mon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>733074</t>
+          <t>820800</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:07</t>
+          <t>2026-07-27 12:19:46</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>치즈</t>
+          <t>도국</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -1070,31 +1062,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>귀촌리</t>
+          <t>기생번식</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=822573&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=845885&amp;tab=mon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>822573</t>
+          <t>845885</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:07</t>
+          <t>2026-07-27 12:19:46</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>황양</t>
+          <t>바쉬</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1162,31 +1154,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>소녀의 세계</t>
+          <t>요리사가 되고 싶은 천마님</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=654774&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=823536&amp;tab=mon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>654774</t>
+          <t>823536</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:07</t>
+          <t>2026-07-27 12:19:46</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>모랑지</t>
+          <t>턍</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1254,31 +1246,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>똑 닮은 딸</t>
+          <t>뻐꾸기는 운다</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=774866&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=850661&amp;tab=mon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>774866</t>
+          <t>850661</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:07</t>
+          <t>2026-07-27 12:19:46</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>이담</t>
+          <t>진요</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1346,46 +1338,38 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>파브르 in 사천당가</t>
+          <t>누가 죄인인가</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=833702&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846782&amp;tab=mon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>833702</t>
+          <t>846782</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:07</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>지대공마법소년</t>
-        </is>
-      </c>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>mon</t>
@@ -1438,31 +1422,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>회귀한 공작가의 막내도련님은 암살자</t>
+          <t>양심과외</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=821195&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=847903&amp;tab=mon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>821195</t>
+          <t>847903</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:07</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>스윙뱃</t>
+          <t>리나</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1530,38 +1514,46 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>그린스킨</t>
+          <t>어떻게 용사 이름이 아아아아</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851187&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=842370&amp;tab=mon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>851187</t>
+          <t>842370</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:08</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>알그</t>
+        </is>
+      </c>
       <c r="I12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>mon</t>
@@ -1614,31 +1606,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>세림의 철칙</t>
+          <t>마왕의 빛나는 별</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852516&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=843072&amp;tab=mon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>852516</t>
+          <t>843072</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:08</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>세윤</t>
+          <t>이잉간</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1706,31 +1698,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>시간을 돌아온 황후의 납치 결혼</t>
+          <t>오매불망</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=834548&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849508&amp;tab=mon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>834548</t>
+          <t>849508</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:09</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>그리온</t>
+          <t>2L</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1798,31 +1790,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>공주는 헬스장에 간다</t>
+          <t>언스탯</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852173&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846057&amp;tab=mon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>852173</t>
+          <t>846057</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:09</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>콕</t>
+          <t>쏜</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1881,40 +1873,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>내가 죽인 드래곤과 결혼했다</t>
+          <t>불완전한 이혼의 결말</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852628&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=838556&amp;tab=mon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>852628</t>
+          <t>838556</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:12</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>만둣불</t>
+          <t>진원</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1932,12 +1924,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1973,40 +1965,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>아폴론 저축은행</t>
+          <t>NPC를 죽였다</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=842845&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846079&amp;tab=mon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>842845</t>
+          <t>846079</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:14</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>차무진</t>
+          <t>무공</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2024,12 +2016,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2065,40 +2057,40 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>다 때려치고 콜라 팝니다</t>
+          <t>게임마스터</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852631&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=832104&amp;tab=mon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>852631</t>
+          <t>832104</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:15</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>윤재호</t>
+          <t>둥치</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2116,12 +2108,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2157,40 +2149,40 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>불로남친</t>
+          <t>지유지요</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852783&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=838532&amp;tab=mon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>852783</t>
+          <t>838532</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:17</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>율로</t>
+          <t>용현동</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2208,12 +2200,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2249,40 +2241,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>코너트 성 집사로 살아남기</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=844064&amp;tab=mon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>844064</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:17</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>LICO</t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2295,17 +2287,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2319,36 +2311,16 @@
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -2361,55 +2333,63 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>럭키비치</t>
+          <t>프로젝트 마르스</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=837999&amp;tab=mon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>852498</t>
+          <t>837999</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:19</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>영주</t>
+        </is>
+      </c>
       <c r="I21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>thu,sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>thu,sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2445,40 +2425,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>좋은 하루 보내</t>
+          <t>네 앞에서만 부끄러운 나는</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852274&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=845496&amp;tab=mon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>852274</t>
+          <t>845496</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:22</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>한구</t>
+          <t>김현아</t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2496,12 +2476,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2537,12 +2517,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2550,27 +2530,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>삼이는 재생한다</t>
+          <t>너의 완두콩을 먹고 싶어!</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=822874&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=839082&amp;tab=mon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>822874</t>
+          <t>839082</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:22</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>강은영</t>
+          <t>니소라스</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2588,12 +2568,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2629,40 +2609,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>일립예고 학생들</t>
+          <t>ZD</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=812962&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=835698&amp;tab=mon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>812962</t>
+          <t>835698</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:23</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>백본</t>
+          <t>조석</t>
         </is>
       </c>
       <c r="I24" t="b">
@@ -2680,12 +2660,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2721,40 +2701,40 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>싸움 1티어 과외 쌤 구하기</t>
+          <t>꽃과 재</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852547&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=848711&amp;tab=mon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>852547</t>
+          <t>848711</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:26</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>버퍼링</t>
+          <t>우루</t>
         </is>
       </c>
       <c r="I25" t="b">
@@ -2772,12 +2752,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2813,40 +2793,40 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>황제의 검</t>
+          <t>함부로 친절하지 말라</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=813443&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=821095&amp;tab=mon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>813443</t>
+          <t>821095</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:30</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>레드훅</t>
+          <t>아린</t>
         </is>
       </c>
       <c r="I26" t="b">
@@ -2864,12 +2844,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2905,40 +2885,40 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>머저리 M수생</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=845214&amp;tab=mon</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>845214</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:30</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>아이아리</t>
         </is>
       </c>
       <c r="I27" t="b">
@@ -2951,17 +2931,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2975,36 +2955,16 @@
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -3017,40 +2977,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>오싹한 연애</t>
+          <t>부두슬램</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852570&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=842462&amp;tab=mon</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>852570</t>
+          <t>842462</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:31</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>꼉</t>
+          <t>도바Q</t>
         </is>
       </c>
       <c r="I28" t="b">
@@ -3068,12 +3028,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3109,55 +3069,63 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>럭키비치</t>
+          <t>주희의 주위</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852498&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849058&amp;tab=mon</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>852498</t>
+          <t>849058</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:32</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
       <c r="I29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>thu,sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>thu,sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3193,40 +3161,40 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>인간의 식탁</t>
+          <t>나의 보이소프렌드</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852761&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=819698&amp;tab=mon</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>852761</t>
+          <t>819698</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:33</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>김규삼</t>
+          <t>망공이</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -3244,12 +3212,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3285,40 +3253,40 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mickey x F1 정상을 향한 질주</t>
+          <t>최강고</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=845837&amp;tab=mon</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>849113</t>
+          <t>845837</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-20 12:20:35</t>
+          <t>2026-07-27 12:19:47</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Brandon Chen</t>
+          <t>공이</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -3336,12 +3304,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3355,42 +3323,2934 @@
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr">
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>101</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>유체를 이탈하였습니다</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=851839&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>851839</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>이슬</t>
+        </is>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>102</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>달로 만든 아이</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=784107&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>784107</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>온윤</t>
+        </is>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>103</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>귀신이 곡할 노릇</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849480&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>849480</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>배아령</t>
+        </is>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>104</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>한국에서 히어로 하기 힘들더라</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=829666&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>829666</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>이해력</t>
+        </is>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>105</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>아직 제목 없음</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=831547&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>831547</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>주영현</t>
+        </is>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>106</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>솔로스쿨</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=824208&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>824208</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>랑쓰</t>
+        </is>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>107</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>비터사이드 크렌베리스</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=841755&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>841755</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>챠콜</t>
+        </is>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>108</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>데빌 캐피탈</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846866&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>846866</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>정민용</t>
+        </is>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>109</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>철이 없어서 그래</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=847435&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>847435</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>심도수</t>
+        </is>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>110</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>웅녀님이 보우하사</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=842322&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>842322</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:47</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>영파카</t>
+        </is>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>111</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>사이다걸</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=800333&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>800333</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:48</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>김드루</t>
+        </is>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>112</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>슬로우 다이브</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=839087&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>839087</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:48</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>고다</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>113</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>두번째 신의아이</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=827318&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>827318</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:48</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>나는야사과될거야</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>114</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>좋아하면 닮는댔어</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=842184&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>842184</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:48</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>문주</t>
+        </is>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>115</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>연애복붙</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=833414&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>833414</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:48</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>석한</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>116</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Lv.99 흑염의 프린세스</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=838075&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>838075</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:48</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>YDR</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>117</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>킬링가드</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853116&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>853116</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:48</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>이제환</t>
+        </is>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>118</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>부활성녀</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853115&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>853115</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:48</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>사리앵</t>
+        </is>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>63</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>남자가 되기 싫어</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852887&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>852887</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:50</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>성은</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>69</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>타락면역이라 재앙급 마검 들고 시작한다</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853004&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>853004</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:50</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>김상민</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>83</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>44교시 생존수업</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=836848&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>836848</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:50</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>상C</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>42</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>멸귀수도전</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=851689&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>851689</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>이산책</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>79</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>찬란한 유산 단편집</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>849862</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:53</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>수, 토 연재</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr">
         <is>
           <t>no_result</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
         <is>
           <t>needs_series_search</t>
         </is>
       </c>
-      <c r="AJ31" t="b">
+      <c r="AJ54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>17</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>홍은영의 이집트 신화</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853034&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>853034</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:55</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>조수현</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>43</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>강남싱크</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852904&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>852904</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:55</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>필원</t>
+        </is>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>40</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>곤륜에 용이 산다</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852601&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>852601</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:19:59</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>정범구</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>115</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>공동급식구역</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=817927&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>817927</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:01</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>청건</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>69</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>찬란한 유산 단편집</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>849862</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:04</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>수, 토 연재</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>112</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>다시, 순정퀘스트</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852275&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>852275</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:05</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>이온도</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>38</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>프롤로그에서 30년이 흘렀다</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852765&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>852765</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:07</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>기린그린</t>
+        </is>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>101</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Mickey x F1 정상을 향한 질주</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>849113</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:20:09</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Brandon Chen</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ62" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/weekly_mapping_recheck_targets.xlsx
+++ b/data/weekly_mapping_recheck_targets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AJ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,40 +601,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>스타코인</t>
+          <t>헬 로그인</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=851412&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853159&amp;tab=wed</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>851412</t>
+          <t>853159</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-03 11:55:55</t>
+          <t>2026-08-10 10:54:07</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>지나무</t>
+          <t>보고싶었어요</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -652,12 +652,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -693,40 +693,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>저 그런 인재 아닙니다</t>
+          <t>찬란한 유산 단편집</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=802840&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>802840</t>
+          <t>849862</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-03 11:55:56</t>
+          <t>2026-08-10 10:54:08</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>에몽</t>
+          <t>네이버웹툰</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -739,17 +739,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>수, 토 연재</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -763,16 +763,36 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="Y3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -785,40 +805,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>언플러그드 보이</t>
+          <t>화림신필</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852504&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852506&amp;tab=thu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>852504</t>
+          <t>852506</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-03 11:55:58</t>
+          <t>2026-08-10 10:54:10</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>천계영</t>
+          <t>레다판다</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -836,12 +856,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -877,40 +897,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>경계선</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=838217&amp;tab=thu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>838217</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-03 11:55:59</t>
+          <t>2026-08-10 10:54:11</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>파트</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -923,17 +943,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -947,36 +967,16 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -989,40 +989,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>연애 전공 새내기입니다</t>
+          <t>미술 연작</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852623&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853280&amp;tab=fri</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>852623</t>
+          <t>853280</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-03 11:55:59</t>
+          <t>2026-08-10 10:54:14</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>교진</t>
+          <t>설이</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1081,40 +1081,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>흑사</t>
+          <t>찬란한 유산 단편집</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=828170&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>828170</t>
+          <t>849862</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-03 11:55:59</t>
+          <t>2026-08-10 10:54:18</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>안경알</t>
+          <t>네이버웹툰</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1127,17 +1127,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>수, 토 연재</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1151,16 +1151,36 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI7" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1173,40 +1193,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>전직지존</t>
+          <t>나랑 같이살아</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852845&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853327&amp;tab=sat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>852845</t>
+          <t>853327</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-03 11:56:01</t>
+          <t>2026-08-10 10:54:19</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>KHJ</t>
+          <t>수현</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1224,12 +1244,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1265,40 +1285,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>가난한 영지의 주인이 되어 버렸다</t>
+          <t>천 살 연하 황제가 집착한다</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853073&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=821378&amp;tab=sat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>853073</t>
+          <t>821378</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-03 11:56:05</t>
+          <t>2026-08-10 10:54:20</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>환범</t>
+          <t>이윤희</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1316,12 +1336,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1357,12 +1377,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1370,27 +1390,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>보이스피싱인데 인생역전</t>
+          <t>리히트</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=830144&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853411&amp;tab=sun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>830144</t>
+          <t>853411</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-03 11:56:06</t>
+          <t>2026-08-10 10:54:22</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>왓더헬</t>
+          <t>용과</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1408,12 +1428,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1449,40 +1469,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>아이돌리</t>
+          <t>Mickey x F1 정상을 향한 질주</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=840875&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>840875</t>
+          <t>849113</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-03 11:56:07</t>
+          <t>2026-08-10 10:54:23</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>로로</t>
+          <t>Brandon Chen</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1500,12 +1520,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1519,338 +1539,42 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI11" t="inlineStr">
         <is>
           <t>needs_series_search</t>
         </is>
       </c>
       <c r="AJ11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>70</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>찬란한 유산 단편집</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>849862</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:09</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>네이버웹툰</t>
-        </is>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>수, 토 연재</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>wed,sat</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>wed,sat</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>81</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>살인 알고리즘</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853270&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>853270</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:13</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>삼수</t>
-        </is>
-      </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>98</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Mickey x F1 정상을 향한 질주</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>849113</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:56:13</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Brandon Chen</t>
-        </is>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ14" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/weekly_mapping_recheck_targets.xlsx
+++ b/data/weekly_mapping_recheck_targets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,40 +601,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>헬 로그인</t>
+          <t>기로의 밤</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853159&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853687&amp;tab=mon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>853159</t>
+          <t>853687</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-10 10:54:07</t>
+          <t>2026-08-17 10:20:10</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>보고싶었어요</t>
+          <t>DOCI</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -652,12 +652,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -693,40 +693,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>함부로 친절하지 말라</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=821095&amp;tab=mon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>821095</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-10 10:54:08</t>
+          <t>2026-08-17 10:20:10</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>아린</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -739,17 +739,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -763,36 +763,16 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -805,40 +785,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>화림신필</t>
+          <t>요리사가 되고 싶은 천마님</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852506&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=823536&amp;tab=mon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>852506</t>
+          <t>823536</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-10 10:54:10</t>
+          <t>2026-08-17 10:20:10</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>레다판다</t>
+          <t>턍</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -856,12 +836,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -897,40 +877,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>경계선</t>
+          <t>킬링가드</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=838217&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853116&amp;tab=mon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>838217</t>
+          <t>853116</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-10 10:54:11</t>
+          <t>2026-08-17 10:20:10</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>파트</t>
+          <t>이제환</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -948,12 +928,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -989,40 +969,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>미술 연작</t>
+          <t>기생번식</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853280&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=845885&amp;tab=mon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>853280</t>
+          <t>845885</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-10 10:54:14</t>
+          <t>2026-08-17 10:20:10</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>설이</t>
+          <t>바쉬</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -1040,12 +1020,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1081,40 +1061,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>마왕의 빛나는 별</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=843072&amp;tab=mon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>843072</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-10 10:54:18</t>
+          <t>2026-08-17 10:20:10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>이잉간</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1127,17 +1107,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1151,36 +1131,16 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1193,40 +1153,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>나랑 같이살아</t>
+          <t>양심과외</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853327&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=847903&amp;tab=mon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>853327</t>
+          <t>847903</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-10 10:54:19</t>
+          <t>2026-08-17 10:20:10</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>수현</t>
+          <t>리나</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1244,12 +1204,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1285,40 +1245,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>천 살 연하 황제가 집착한다</t>
+          <t>어떻게 용사 이름이 아아아아</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=821378&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=842370&amp;tab=mon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>821378</t>
+          <t>842370</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-10 10:54:20</t>
+          <t>2026-08-17 10:20:10</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>이윤희</t>
+          <t>알그</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1336,12 +1296,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1377,40 +1337,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>리히트</t>
+          <t>언스탯</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853411&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846057&amp;tab=mon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>853411</t>
+          <t>846057</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-10 10:54:22</t>
+          <t>2026-08-17 10:20:10</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>용과</t>
+          <t>쏜</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1428,12 +1388,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1469,63 +1429,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mickey x F1 정상을 향한 질주</t>
+          <t>누가 죄인인가</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846782&amp;tab=mon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>849113</t>
+          <t>846782</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-10 10:54:23</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Brandon Chen</t>
-        </is>
-      </c>
+          <t>2026-08-17 10:20:10</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1539,42 +1491,4122 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr">
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>82</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>오매불망</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849508&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>849508</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:10</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2L</t>
+        </is>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>83</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NPC를 죽였다</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846079&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>846079</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:10</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>무공</t>
+        </is>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>85</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>뻐꾸기는 운다</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=850661&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>850661</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:10</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>진요</t>
+        </is>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>86</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lv.99 흑염의 프린세스</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=838075&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>838075</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:10</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>YDR</t>
+        </is>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>87</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>반도대탈출</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=851869&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>851869</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:10</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>카시모프</t>
+        </is>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>88</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>불완전한 이혼의 결말</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=838556&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>838556</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:10</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>진원</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>89</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>게임마스터</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=832104&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>832104</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:10</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>둥치</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>프로젝트 마르스</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=837999&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>837999</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:10</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>영주</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>91</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>네 앞에서만 부끄러운 나는</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=845496&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>845496</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:10</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>김현아</t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>92</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>지유지요</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=838532&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>838532</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>용현동</t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>93</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>코너트 성 집사로 살아남기</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=844064&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>844064</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>LICO</t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>94</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>머저리 M수생</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=845214&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>845214</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>규정</t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>95</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>꽃과 재</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=848711&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>848711</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>우루</t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>96</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>너의 완두콩을 먹고 싶어!</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=839082&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>839082</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>니소라스</t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>97</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>한국에서 히어로 하기 힘들더라</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=829666&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>829666</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>이해력</t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>98</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>나의 보이소프렌드</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=819698&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>819698</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>망공이</t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>99</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>최강고</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=845837&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>845837</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>공이</t>
+        </is>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>100</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>주희의 주위</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849058&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>849058</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>101</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>아직 제목 없음</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=831547&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>831547</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>주영현</t>
+        </is>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>102</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>솔로스쿨</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=824208&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>824208</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>랑쓰</t>
+        </is>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>103</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>귀신이 곡할 노릇</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849480&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>849480</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>배아령</t>
+        </is>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>104</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>달로 만든 아이</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=784107&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>784107</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>온윤</t>
+        </is>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>105</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>비터사이드 크렌베리스</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=841755&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>841755</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>챠콜</t>
+        </is>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>106</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>데빌 캐피탈</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846866&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>846866</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>정민용</t>
+        </is>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>107</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>웅녀님이 보우하사</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=842322&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>842322</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>영파카</t>
+        </is>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>108</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>철이 없어서 그래</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=847435&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>847435</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>심도수</t>
+        </is>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>109</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>유체를 이탈하였습니다</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=851839&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>851839</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>이슬</t>
+        </is>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>110</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>슬로우 다이브</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=839087&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>839087</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>고다</t>
+        </is>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>111</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>좋아하면 닮는댔어</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=842184&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>842184</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>문주</t>
+        </is>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>112</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>연애복붙</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=833414&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>833414</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>석한</t>
+        </is>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>113</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>생존지상주의</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853709&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>853709</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>토이</t>
+        </is>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>114</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>28, 청춘!</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853838&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>853838</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:11</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>이나라</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>53</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>그랬더니 남친임니다</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853326&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>853326</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:13</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>뽀꼬</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>화, 금 연재</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>80</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>우리 커플 아님!</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853820&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>853820</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:18</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>봄소희</t>
+        </is>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>81</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>찬란한 유산 단편집</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>849862</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:18</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>수, 토 연재</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr">
         <is>
           <t>no_result</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
         <is>
           <t>needs_series_search</t>
         </is>
       </c>
-      <c r="AJ11" t="b">
+      <c r="AJ46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>34</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>나의 경험</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853278&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>853278</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:20</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>105</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>카루나</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=754876&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>754876</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:22</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>강호진</t>
+        </is>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>48</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>그랬더니 남친임니다</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853326&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>853326</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:23</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>뽀꼬</t>
+        </is>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>화, 금 연재</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>14</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>호랑이형님</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=650305&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>650305</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:26</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>이상규</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>79</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>찬란한 유산 단편집</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>849862</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:28</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>수, 토 연재</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>86</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>악몽무당</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853837&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>853837</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:33</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>공현곤</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>92</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>악녀의 시집살이는 즐겁다</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853972&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>853972</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:33</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>최무탁</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>100</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Mickey x F1 정상을 향한 질주</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>849113</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:33</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Brandon Chen</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>101</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>방문을 열면 그곳엔 괴물</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=845387&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>845387</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:20:33</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>긴편지</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ55" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/weekly_mapping_recheck_targets.xlsx
+++ b/data/weekly_mapping_recheck_targets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ16"/>
+  <dimension ref="A1:AJ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,40 +601,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>공포 쯔꾸르 생존기</t>
+          <t>역변! 첫사랑</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854133&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853903&amp;tab=tue</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>854133</t>
+          <t>853903</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-24 10:21:52</t>
+          <t>2026-08-31 13:16:36</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LICO</t>
+          <t>혁상</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -652,12 +652,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -702,31 +702,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>인간은 썩었어</t>
+          <t>심판</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853936&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852505&amp;tab=tue</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>853936</t>
+          <t>852505</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-24 10:21:54</t>
+          <t>2026-08-31 13:16:36</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>차흐</t>
+          <t>뿌엑이</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -794,31 +794,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>후원 낙인</t>
+          <t>아름다운 줄리엣을 위하여</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853895&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=829139&amp;tab=tue</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>853895</t>
+          <t>829139</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-24 10:21:54</t>
+          <t>2026-08-31 13:16:37</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>송의영</t>
+          <t>나사못</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -886,38 +886,46 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>숙녀가 대머리이면 어떻단말인가</t>
+          <t>원더랜드</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853619&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852503&amp;tab=wed</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>853619</t>
+          <t>852503</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-24 10:21:57</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>2026-08-31 13:16:38</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>까말솔</t>
+        </is>
+      </c>
       <c r="I5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>wed</t>
@@ -970,31 +978,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>해일주의보</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853833&amp;tab=wed</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>853833</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-24 10:21:58</t>
+          <t>2026-08-31 13:16:39</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>맛곰</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -1007,17 +1015,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1031,36 +1039,16 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1082,31 +1070,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>은빛 눈이 반짝이던</t>
+          <t>찬란한 유산 단편집</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853653&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>853653</t>
+          <t>849862</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-24 10:21:58</t>
+          <t>2026-08-31 13:16:40</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>조이은</t>
+          <t>네이버웹툰</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1119,17 +1107,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>수, 토 연재</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1143,16 +1131,36 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI7" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1174,31 +1182,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>나의 죄</t>
+          <t>까맣지만 새하얀</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853249&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854126&amp;tab=thu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>853249</t>
+          <t>854126</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:00</t>
+          <t>2026-08-31 13:16:42</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>젤리피쉬</t>
+          <t>최준영</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1266,31 +1274,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>게임 속 바바리안으로 살아남기</t>
+          <t>개는 헤엄치는 꿈을 꾼다</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=808482&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854250&amp;tab=thu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>808482</t>
+          <t>854250</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:00</t>
+          <t>2026-08-31 13:16:43</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>팀 더 지크</t>
+          <t>권</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1358,31 +1366,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>오답 없는 방정식</t>
+          <t>감히, 내가 너를</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854036&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854088&amp;tab=fri</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>854036</t>
+          <t>854088</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:04</t>
+          <t>2026-08-31 13:16:47</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>곰지공</t>
+          <t>이끼끼</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1450,54 +1458,46 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>초임계지옥</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854340&amp;tab=sat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>854340</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:07</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>네이버웹툰</t>
-        </is>
-      </c>
+          <t>2026-08-31 13:16:50</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>수, 토 연재</t>
-        </is>
-      </c>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1511,36 +1511,16 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1562,31 +1542,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>아주 사적인 영역</t>
+          <t>찬란한 유산 단편집</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852616&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>852616</t>
+          <t>849862</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:08</t>
+          <t>2026-08-31 13:16:51</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>숲</t>
+          <t>네이버웹툰</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1599,17 +1579,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>수, 토 연재</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1623,16 +1603,36 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI12" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1654,31 +1654,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>차라리 빌런으로 살겠다</t>
+          <t>모두가 날 싫어한다</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=842601&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=843426&amp;tab=sat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>842601</t>
+          <t>843426</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:08</t>
+          <t>2026-08-31 13:16:52</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>덤보</t>
+          <t>산하</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1746,38 +1746,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>지옥심판</t>
+          <t>귀농했더니 국가급 거물 후배들이 몰려든다</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854096&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853943&amp;tab=sun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>854096</t>
+          <t>853943</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:10</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>2026-08-31 13:16:54</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>우기</t>
+        </is>
+      </c>
       <c r="I14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>sun</t>
@@ -1830,38 +1838,46 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>꿈에서 본 그놈이 대단해!</t>
+          <t>엄마는 돼지가 되었다</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854132&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854129&amp;tab=sun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>854132</t>
+          <t>854129</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:11</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>2026-08-31 13:16:55</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>사자베기</t>
+        </is>
+      </c>
       <c r="I15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>sun</t>
@@ -1918,27 +1934,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mickey x F1 정상을 향한 질주</t>
+          <t>고백대리</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=838945&amp;tab=sun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>849113</t>
+          <t>838945</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-24 10:22:11</t>
+          <t>2026-08-31 13:16:56</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Brandon Chen</t>
+          <t>문조</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1975,42 +1991,134 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr">
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>104</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mickey x F1 정상을 향한 질주</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>849113</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:16:56</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Brandon Chen</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>no_result</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
         <is>
           <t>needs_series_search</t>
         </is>
       </c>
-      <c r="AJ16" t="b">
+      <c r="AJ17" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/weekly_mapping_recheck_targets.xlsx
+++ b/data/weekly_mapping_recheck_targets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ17"/>
+  <dimension ref="A1:AJ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,40 +601,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>역변! 첫사랑</t>
+          <t>천마 아포칼립스</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853903&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854152&amp;tab=mon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>853903</t>
+          <t>854152</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:36</t>
+          <t>2026-09-07 12:24:56</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>혁상</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -652,12 +652,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -693,40 +693,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>심판</t>
+          <t>방과후 짝사랑 시네마</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852505&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854366&amp;tab=mon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>852505</t>
+          <t>854366</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:36</t>
+          <t>2026-09-07 12:24:56</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>뿌엑이</t>
+          <t>미킴</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -744,12 +744,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -785,40 +785,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>아름다운 줄리엣을 위하여</t>
+          <t>2026 루키 단편선</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=829139&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=mon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>829139</t>
+          <t>853869</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:37</t>
+          <t>2026-09-07 12:24:56</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>나사못</t>
+          <t>네이버웹툰</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -831,17 +831,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>월, 수, 목, 일 연재</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon,wed,thu,sun</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon,wed,thu,sun</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -877,40 +877,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>원더랜드</t>
+          <t>기생번식</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852503&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=845885&amp;tab=mon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>852503</t>
+          <t>845885</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:38</t>
+          <t>2026-09-07 12:24:56</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>까말솔</t>
+          <t>바쉬</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -928,12 +928,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -969,40 +969,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>해일주의보</t>
+          <t>양심과외</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853833&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=847903&amp;tab=mon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>853833</t>
+          <t>847903</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:39</t>
+          <t>2026-09-07 12:24:57</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>맛곰</t>
+          <t>리나</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1061,40 +1061,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>Lv.99 흑염의 프린세스</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=838075&amp;tab=mon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>838075</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:40</t>
+          <t>2026-09-07 12:24:57</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>YDR</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1131,36 +1131,16 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1173,40 +1153,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>까맣지만 새하얀</t>
+          <t>마왕의 빛나는 별</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854126&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=843072&amp;tab=mon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>854126</t>
+          <t>843072</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:42</t>
+          <t>2026-09-07 12:24:57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>최준영</t>
+          <t>이잉간</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1224,12 +1204,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1265,40 +1245,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>개는 헤엄치는 꿈을 꾼다</t>
+          <t>헤어져서 팝니다</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854250&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=850709&amp;tab=mon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>854250</t>
+          <t>850709</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:43</t>
+          <t>2026-09-07 12:24:57</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>권</t>
+          <t>헛둘</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1316,12 +1296,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1357,40 +1337,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>감히, 내가 너를</t>
+          <t>어떻게 용사 이름이 아아아아</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854088&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=842370&amp;tab=mon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>854088</t>
+          <t>842370</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:47</t>
+          <t>2026-09-07 12:24:57</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>이끼끼</t>
+          <t>알그</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1408,12 +1388,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1449,55 +1429,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>초임계지옥</t>
+          <t>언스탯</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854340&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846057&amp;tab=mon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>854340</t>
+          <t>846057</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:50</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>쏜</t>
+        </is>
+      </c>
       <c r="I11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1533,40 +1521,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>찬란한 유산 단편집</t>
+          <t>마귀공주</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852115&amp;tab=mon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>849862</t>
+          <t>852115</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:51</t>
+          <t>2026-09-07 12:24:57</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>햄스터빵디</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1579,17 +1567,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1603,36 +1591,16 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1645,63 +1613,55 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>모두가 날 싫어한다</t>
+          <t>누가 죄인인가</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=843426&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846782&amp;tab=mon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>843426</t>
+          <t>846782</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:52</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>산하</t>
-        </is>
-      </c>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1737,40 +1697,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>귀농했더니 국가급 거물 후배들이 몰려든다</t>
+          <t>오매불망</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853943&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849508&amp;tab=mon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>853943</t>
+          <t>849508</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:54</t>
+          <t>2026-09-07 12:24:57</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>우기</t>
+          <t>2L</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1788,12 +1748,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1829,40 +1789,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>엄마는 돼지가 되었다</t>
+          <t>28, 청춘!</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854129&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853838&amp;tab=mon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>854129</t>
+          <t>853838</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:55</t>
+          <t>2026-09-07 12:24:57</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>사자베기</t>
+          <t>이나라</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1880,12 +1840,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1921,40 +1881,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>고백대리</t>
+          <t>NPC를 죽였다</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=838945&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846079&amp;tab=mon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>838945</t>
+          <t>846079</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:56</t>
+          <t>2026-09-07 12:24:57</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>문조</t>
+          <t>무공</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1972,12 +1932,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2013,40 +1973,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mickey x F1 정상을 향한 질주</t>
+          <t>게임마스터</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=832104&amp;tab=mon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>849113</t>
+          <t>832104</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-08-31 13:16:56</t>
+          <t>2026-09-07 12:24:57</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Brandon Chen</t>
+          <t>둥치</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2064,12 +2024,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2083,42 +2043,4390 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr">
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>89</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>공주는 헬스장에 간다</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852173&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>852173</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>콕</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>꽃과 재</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=848711&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>848711</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>우루</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>91</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>코너트 성 집사로 살아남기</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=844064&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>844064</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>LICO</t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>92</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>불완전한 이혼의 결말</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=838556&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>838556</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>진원</t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>93</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>나의 보이소프렌드</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=819698&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>819698</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>망공이</t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>94</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>프로젝트 마르스</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=837999&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>837999</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>영주</t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>95</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>지유지요</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=838532&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>838532</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>용현동</t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>96</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>네 앞에서만 부끄러운 나는</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=845496&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>845496</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>김현아</t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>97</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>뻐꾸기는 운다</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=850661&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>850661</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>진요</t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>98</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>머저리 M수생</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=845214&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>845214</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>규정</t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>99</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>한국에서 히어로 하기 힘들더라</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=829666&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>829666</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>이해력</t>
+        </is>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>100</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>너의 완두콩을 먹고 싶어!</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=839082&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>839082</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>니소라스</t>
+        </is>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>101</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>주희의 주위</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849058&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>849058</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>102</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>비터사이드 크렌베리스</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=841755&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>841755</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>챠콜</t>
+        </is>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>103</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>달로 만든 아이</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=784107&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>784107</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>온윤</t>
+        </is>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>104</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>솔로스쿨</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=824208&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>824208</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>랑쓰</t>
+        </is>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>105</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>귀신이 곡할 노릇</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849480&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>849480</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>배아령</t>
+        </is>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>106</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>아직 제목 없음</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=831547&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>831547</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>주영현</t>
+        </is>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>107</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>반도대탈출</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=851869&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>851869</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>카시모프</t>
+        </is>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>108</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>최강고</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=845837&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>845837</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>공이</t>
+        </is>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>109</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>데빌 캐피탈</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846866&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>846866</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:57</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>정민용</t>
+        </is>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>110</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>웅녀님이 보우하사</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=842322&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>842322</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:58</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>영파카</t>
+        </is>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>111</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>철이 없어서 그래</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=847435&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>847435</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:58</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>심도수</t>
+        </is>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>112</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>슬로우 다이브</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=839087&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>839087</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:58</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>고다</t>
+        </is>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>113</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>좋아하면 닮는댔어</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=842184&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>842184</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:58</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>문주</t>
+        </is>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>114</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>유체를 이탈하였습니다</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=851839&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>851839</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:58</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>이슬</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>115</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>마왕의 친구</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854402&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>854402</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:58</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>스컬리</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>116</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>채널명 : 구찬지아</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=841486&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>841486</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:58</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>김기현</t>
+        </is>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>36</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>괴력 난신</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=821597&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>821597</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:24:59</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>매드버드</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>102</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>사표내고 이계에서 힐링합니다</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=800726&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>800726</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>덤보</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>112</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>긁지 않은 복권</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=828908&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>828908</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:01</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>보로리</t>
+        </is>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>71</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026 루키 단편선</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>853869</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:03</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>월, 수, 목, 일 연재</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>mon,wed,thu,sun</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>mon,wed,thu,sun</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>79</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>헤르몬트 공작의 남자 정부</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854343&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>854343</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:03</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>몽찌</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>80</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>찬란한 유산 단편집</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>849862</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:03</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>수, 토 연재</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr">
         <is>
           <t>no_result</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
         <is>
           <t>needs_series_search</t>
         </is>
       </c>
-      <c r="AJ17" t="b">
+      <c r="AJ51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>92</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>계약 결혼 종료</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=839331&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>839331</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:03</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>꾸리</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>56</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>월스트리트 천재의 시한부 투자법</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854407&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>854407</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:06</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>박성현</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>70</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026 루키 단편선</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>853869</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:06</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>월, 수, 목, 일 연재</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>mon,wed,thu,sun</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>mon,wed,thu,sun</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>90</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>서울밤피어</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=807537&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>807537</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:07</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>송지형</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>49</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>사랑은 좀비를 찢고</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854591&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>854591</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:09</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>투현</t>
+        </is>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>70</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>찬란한 유산 단편집</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849862&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>849862</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:13</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>수, 토 연재</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>95</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>남편이 아이를 숨겼다</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854412&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>854412</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:14</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>개굴</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>104</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>탑아이돌의 막내 멤버가 되었다</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=819748&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>819748</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:14</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>맛곰</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>113</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>살아생전</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=832575&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>832575</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:14</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>지도</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>66</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>인터뷰</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854396&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>854396</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:16</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>67</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026 루키 단편선</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>853869</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:16</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>월, 수, 목, 일 연재</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>mon,wed,thu,sun</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>mon,wed,thu,sun</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>77</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>나의 비발디</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=854344&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>854344</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:16</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>105</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Mickey x F1 정상을 향한 질주</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>849113</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:25:17</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Brandon Chen</t>
+        </is>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ64" t="b">
         <v>1</v>
       </c>
     </row>
